--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,7 +650,7 @@
     <t>NutritionOrder.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -678,7 +678,7 @@
     <t>NutritionOrder.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -728,7 +728,7 @@
     <t>NutritionOrder.orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -753,7 +753,7 @@
     <t>NutritionOrder.allergyIntolerance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(AllergyIntolerance|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/allergyintolerance-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1707,7 +1707,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.1328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-nutritionorder-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,6 +455,27 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>NutritionOrder.extension:cosigner</t>
+  </si>
+  <si>
+    <t>cosigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/resource-cosigner}
+</t>
+  </si>
+  <si>
+    <t>Individual who co-signed or verified this nutrition order</t>
+  </si>
+  <si>
+    <t>Identifies an individual who reviewed, verified, or co-signed the associated
+clinical document, note, order, or healthcare record, alongside the primary author or requester.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>NutritionOrder.extension:additionalInfo</t>
   </si>
   <si>
@@ -471,10 +492,6 @@
     <t>Applied at the root level of any resource. Used to capture supplementary
 or non-standard information related to a FHIR resource that is not
 represented by the core FHIR elements or existing profiles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>NutritionOrder.modifierExtension</t>
@@ -1694,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN73"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.203125" customWidth="true" bestFit="true"/>
@@ -2784,7 +2801,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2885,11 +2902,13 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2902,26 +2921,22 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -2969,7 +2984,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2978,7 +2993,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -2990,7 +3005,7 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
@@ -2998,14 +3013,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3018,24 +3033,26 @@
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
       </c>
@@ -3083,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3095,27 +3112,27 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3135,19 +3152,19 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3197,7 +3214,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3212,24 +3229,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3252,16 +3269,16 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3311,7 +3328,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3326,13 +3343,13 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -3363,7 +3380,7 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>103</v>
@@ -3374,7 +3391,9 @@
       <c r="M15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N15" s="2"/>
+      <c r="N15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3438,13 +3457,13 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3452,10 +3471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3463,32 +3482,30 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
         <v>183</v>
       </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3513,13 +3530,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3537,13 +3554,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -3552,28 +3569,28 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3595,17 +3612,15 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3629,13 +3644,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3653,7 +3668,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>89</v>
@@ -3668,28 +3683,28 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3702,23 +3717,25 @@
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O18" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3743,13 +3760,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3767,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3782,24 +3799,24 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3807,7 +3824,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3819,19 +3836,21 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3879,10 +3898,10 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3894,24 +3913,24 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3919,7 +3938,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3931,16 +3950,16 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3991,10 +4010,10 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -4006,24 +4025,24 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4031,7 +4050,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4046,13 +4065,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4103,10 +4122,10 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>89</v>
@@ -4118,24 +4137,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4146,7 +4165,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4155,20 +4174,18 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4217,13 +4234,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4232,24 +4249,24 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4272,16 +4289,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4307,13 +4324,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4331,7 +4348,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4349,10 +4366,10 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4360,10 +4377,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4386,16 +4403,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4421,31 +4438,31 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4463,10 +4480,10 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
@@ -4474,10 +4491,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4488,7 +4505,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4500,15 +4517,17 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4533,13 +4552,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4557,16 +4576,16 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>101</v>
@@ -4575,10 +4594,10 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4586,10 +4605,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4612,13 +4631,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4669,7 +4688,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4678,19 +4697,19 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4698,21 +4717,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4724,7 +4743,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>271</v>
@@ -4732,9 +4751,7 @@
       <c r="M27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4789,13 +4806,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4804,7 +4821,7 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -4812,14 +4829,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4832,10 +4849,10 @@
         <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>134</v>
@@ -4847,11 +4864,9 @@
         <v>277</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4920,7 +4935,7 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4935,35 +4950,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4987,31 +5006,31 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5023,38 +5042,38 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5063,16 +5082,16 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5099,13 +5118,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5123,7 +5142,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5138,28 +5157,28 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5178,13 +5197,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5235,7 +5254,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5250,7 +5269,7 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>299</v>
@@ -5278,7 +5297,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5290,13 +5309,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5347,28 +5366,28 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5376,21 +5395,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5402,7 +5421,7 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>271</v>
@@ -5410,9 +5429,7 @@
       <c r="M33" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5467,13 +5484,13 @@
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5482,7 +5499,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5490,14 +5507,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5510,10 +5527,10 @@
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>134</v>
@@ -5525,11 +5542,9 @@
         <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5598,7 +5613,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5606,42 +5621,46 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5665,13 +5684,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5689,31 +5708,31 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -5744,13 +5763,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5777,13 +5796,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5816,16 +5835,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37">
@@ -5844,7 +5863,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5856,13 +5875,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5919,7 +5938,7 @@
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -5931,10 +5950,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -5942,10 +5961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5956,7 +5975,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5968,13 +5987,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6025,28 +6044,28 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>322</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6054,21 +6073,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6080,7 +6099,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>271</v>
@@ -6088,9 +6107,7 @@
       <c r="M39" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6145,13 +6162,13 @@
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6160,7 +6177,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6168,14 +6185,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6188,10 +6205,10 @@
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>134</v>
@@ -6203,11 +6220,9 @@
         <v>277</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6276,7 +6291,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6284,44 +6299,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6345,13 +6362,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6369,28 +6386,28 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>283</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6398,10 +6415,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6424,16 +6441,16 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6459,14 +6476,14 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6483,7 +6500,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6498,13 +6515,13 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6512,10 +6529,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6526,7 +6543,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6538,15 +6555,17 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6571,14 +6590,14 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6595,13 +6614,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6610,13 +6629,13 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6624,10 +6643,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6638,7 +6657,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6647,20 +6666,18 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6685,13 +6702,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6709,13 +6726,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6724,13 +6741,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6738,10 +6755,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6752,7 +6769,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6761,18 +6778,20 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6821,25 +6840,25 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>350</v>
@@ -6864,7 +6883,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6876,13 +6895,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>267</v>
+        <v>353</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6933,28 +6952,28 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>269</v>
+        <v>355</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -6962,21 +6981,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6988,7 +7007,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>271</v>
@@ -6996,9 +7015,7 @@
       <c r="M47" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7053,13 +7070,13 @@
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7068,7 +7085,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7076,14 +7093,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7096,10 +7113,10 @@
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>134</v>
@@ -7111,11 +7128,9 @@
         <v>277</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7184,7 +7199,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7192,42 +7207,46 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>281</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7251,13 +7270,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7275,39 +7294,39 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7327,16 +7346,16 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7363,13 +7382,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7387,7 +7406,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7402,35 +7421,35 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>161</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7442,13 +7461,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7499,13 +7518,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -7514,13 +7533,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>367</v>
+        <v>166</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -7535,14 +7554,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7554,7 +7573,7 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>369</v>
@@ -7617,7 +7636,7 @@
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
@@ -7626,13 +7645,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -7640,10 +7659,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7663,20 +7682,18 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7725,7 +7742,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7740,13 +7757,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -7754,10 +7771,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7777,18 +7794,20 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7837,7 +7856,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7846,19 +7865,19 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>378</v>
+        <v>304</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -7892,13 +7911,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>266</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7949,7 +7968,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7958,19 +7977,19 @@
         <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>269</v>
+        <v>384</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -7978,21 +7997,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8004,7 +8023,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>271</v>
@@ -8012,9 +8031,7 @@
       <c r="M56" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N56" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8069,13 +8086,13 @@
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8084,7 +8101,7 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8092,14 +8109,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8112,10 +8129,10 @@
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>134</v>
@@ -8127,11 +8144,9 @@
         <v>277</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8200,7 +8215,7 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -8208,42 +8223,46 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>281</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8267,13 +8286,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8291,39 +8310,39 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>383</v>
+        <v>283</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>388</v>
+        <v>132</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8343,16 +8362,16 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8379,13 +8398,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8403,7 +8422,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8418,24 +8437,24 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>161</v>
+        <v>393</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8458,13 +8477,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8491,13 +8510,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8515,7 +8534,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8530,24 +8549,24 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>397</v>
+        <v>166</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8570,13 +8589,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8603,13 +8622,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8627,7 +8646,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8642,24 +8661,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>132</v>
+        <v>402</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8682,13 +8701,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8739,7 +8758,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8757,10 +8776,10 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>371</v>
+        <v>304</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>404</v>
+        <v>132</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>20</v>
@@ -8768,10 +8787,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8794,13 +8813,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8827,13 +8846,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -8851,7 +8870,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8869,10 +8888,10 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>20</v>
@@ -8880,10 +8899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8894,7 +8913,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -8906,17 +8925,15 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -8941,13 +8958,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8965,13 +8982,13 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
@@ -8983,7 +9000,7 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>416</v>
@@ -9008,7 +9025,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9020,15 +9037,17 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>266</v>
+        <v>418</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9077,28 +9096,28 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>268</v>
+        <v>417</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>269</v>
+        <v>421</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -9106,21 +9125,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9132,7 +9151,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>271</v>
@@ -9140,9 +9159,7 @@
       <c r="M66" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9197,13 +9214,13 @@
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -9212,7 +9229,7 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -9220,14 +9237,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9240,10 +9257,10 @@
         <v>20</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>134</v>
@@ -9255,11 +9272,9 @@
         <v>277</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>20</v>
       </c>
@@ -9328,7 +9343,7 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>132</v>
+        <v>274</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
@@ -9336,42 +9351,46 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>290</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>421</v>
+        <v>281</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -9419,28 +9438,28 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>283</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>423</v>
+        <v>132</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -9448,14 +9467,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9474,13 +9493,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9531,7 +9550,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9546,13 +9565,13 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>371</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -9560,10 +9579,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9586,7 +9605,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>429</v>
+        <v>315</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>430</v>
@@ -9594,9 +9613,7 @@
       <c r="M70" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N70" t="s" s="2">
-        <v>432</v>
-      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9645,7 +9662,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9663,10 +9680,10 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>20</v>
@@ -9674,10 +9691,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9700,7 +9717,7 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>310</v>
+        <v>434</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>435</v>
@@ -9708,7 +9725,9 @@
       <c r="M71" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="N71" s="2"/>
+      <c r="N71" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -9757,7 +9776,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9775,10 +9794,10 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>
@@ -9786,10 +9805,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9809,20 +9828,18 @@
         <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -9871,7 +9888,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9886,13 +9903,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>132</v>
+        <v>442</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -9900,10 +9917,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9914,7 +9931,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -9923,19 +9940,19 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>50</v>
+        <v>444</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>444</v>
+        <v>348</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9985,13 +10002,13 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
@@ -10000,15 +10017,129 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>445</v>
+        <v>349</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>20</v>
       </c>
     </row>
